--- a/02_Data_Dictionary/RetailMart_Data_Dictionary.xlsx
+++ b/02_Data_Dictionary/RetailMart_Data_Dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Projects\Retail_DWH_Project\02_Data_Dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC0310A5-B08C-4A4B-993B-3DAD6C2E6560}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EFCF3B-DAEC-4166-A940-525047C9BFD4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{B3FDB186-0A77-4619-8A83-A7E920472852}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
   <si>
     <t>Column Name</t>
   </si>
@@ -190,6 +190,18 @@
   </si>
   <si>
     <t>Latest record used for deduplication</t>
+  </si>
+  <si>
+    <t>CUSTOMER_STATUS</t>
+  </si>
+  <si>
+    <t>current customer status</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Must be active or inactive</t>
   </si>
 </sst>
 </file>
@@ -582,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AFE4B7A-13D5-42EE-98DC-D984FFEA83C5}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.6328125" style="5" bestFit="1" customWidth="1"/>
@@ -815,41 +827,61 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="8">
-        <v>45667.385416666664</v>
+        <v>56</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="8">
+        <v>45667.385416666664</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E14" s="8">
         <v>45672.479166666664</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>54</v>
       </c>
     </row>
